--- a/data/lh2-database.xlsx
+++ b/data/lh2-database.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,6 +643,70 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Origin of the LH2/MCH/NH3 per-component carrier-cost comparison reproduced in kawasaki-2026-supplemental. Cited second-hand via KHI; primary IAE source not yet held in repo [needs source: primary].</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>doe-2009-h2-liquefaction-energy</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>U.S. DOE Hydrogen and Fuel Cells Program Record #9013 -- Energy Requirements for Hydrogen Gas Compression and Liquefaction as Related to Vehicle Storage Needs (M. Gardiner, 7 Jul 2009; approved S. Satyapal, 26 Oct 2009).</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>institutional</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://www.hydrogen.energy.gov/docs/hydrogenprogramlibraries/pdfs/9013_energy_requirements_for_hydrogen_gas_compression.pdf</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ideal/theoretical minimum specific work to liquefy H2 from ambient (~300K/1 atm) gas to liquid at NBP: ~3.3 kWh/kg (11.9 MJ/kg) normal-H2 basis; ~3.9 kWh/kg (14.2 MJ/kg) with conversion to para-H2 (required for real LH2 storage). Retrieved via web search Jul 2026; direct PDF fetch returned HTTP 403, figures corroborated against independent secondary sources (see hull-2024-orthopara-exergy) [needs source: primary PDF verification].</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hull-2024-orthopara-exergy</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Comparative energy and exergy analysis of ortho-para hydrogen and non-ortho-para hydrogen conversion in hydrogen liquefaction. International Journal of Hydrogen Energy 78 (2024) 991-1003.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>institutional</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://www.sciencedirect.com/science/article/pii/S0360319924026089</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Peer-reviewed cross-check: LH2 exergy content ~=11.5% of its LHV (0.115x33.33 = 3.83 kWh/kg), consistent with doe-2009-h2-liquefaction-energy's ~3.9 kWh/kg para-H2 ideal-work figure. Also cites current-plant SEC 8.45-15.65 kWh/kg range.</t>
         </is>
       </c>
     </row>
@@ -657,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1560,6 +1624,210 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>NOT disclosed by KHI (reply Q11): Feasibility Study necessary</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>liquefier</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>theoretical_min_specific_work_normal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>reversible/ideal exergy; ambient ~300K/1 atm normal-H2 gas -&gt; normal-H2 liquid at NBP ~20.3K, no O-P conversion accounted</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>doe-2009-h2-liquefaction-energy</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>11.9 MJ/kg; textbook ideal-work baseline, not KHI-specific</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>liquefier</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>theoretical_min_specific_work_para</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>as above but product converted to (near-)para-H2, as required for real LH2 storage</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>doe-2009-h2-liquefaction-energy</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>14.2 MJ/kg; cross-checked via hull-2024-orthopara-exergy (LH2 exergy ~=11.5% of LHV -&gt; 3.83 kWh/kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>liquefier</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>khi_second_law_efficiency_normal_basis</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>KHI's disclosed 8-9 kWh/kg vs theoretical_min_specific_work_normal (3.3 kWh/kg)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>derived: eff = ideal/actual, using KHI's own 8-9 kWh/kg range; upper bound only -- see note on feed-pressure basis below</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>liquefier</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>khi_second_law_efficiency_para_basis</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>KHI's disclosed 8-9 kWh/kg vs theoretical_min_specific_work_para (3.9 kWh/kg)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>derived: eff = ideal/actual; fairer basis since KHI's process includes O-P conversion (reply Q6/Q7); KHI did not confirm the feed-pressure basis for its 8-9 kWh/kg figure, so both ranges are upper-bound estimates -- a pressurised feed (e.g. this project's 30 barg assumption) implies a lower true ideal-work baseline and therefore a lower true efficiency than shown here</t>
         </is>
       </c>
     </row>

--- a/data/lh2-database.xlsx
+++ b/data/lh2-database.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1828,6 +1828,55 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>derived: eff = ideal/actual; fairer basis since KHI's process includes O-P conversion (reply Q6/Q7); KHI did not confirm the feed-pressure basis for its 8-9 kWh/kg figure, so both ranges are upper-bound estimates -- a pressurised feed (e.g. this project's 30 barg assumption) implies a lower true ideal-work baseline and therefore a lower true efficiency than shown here</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>liquefier</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>theoretical_min_specific_work_bog_reliquefaction</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>condensation-only exergy: saturated H2 vapor at NBP (~20.3K) -&gt; saturated liquid at NBP, vs 300K ambient dead state</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>doe-2009-h2-liquefaction-energy</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>derived from the same exergy formula/constants as theoretical_min_specific_work_normal/_para, but excluding the sensible-cooling and O-P-conversion terms since BOG starts already cold and near-equilibrium para fraction; excludes any real compression work to route low-pressure BOG into the liquefaction cycle (KHI reply Q3/Q14 ejector/compressor, no separate SEC disclosed)</t>
         </is>
       </c>
     </row>

--- a/data/lh2-database.xlsx
+++ b/data/lh2-database.xlsx
@@ -14,6 +14,7 @@
     <sheet name="lh2_properties" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="lh2_carriers" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="cost_stack" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="chain_energy_defaults" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5564,4 +5565,1645 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>segment</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lower_heating_value</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>33.333</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>120 MJ/kg / 3.6; energy basis for every efficiency in this table</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>mirrors data/properties/lh2-properties.csv; pending NIST/ISO citation approval (docs/memory.md open item 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nh3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>lower_heating_value</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5.167</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>18.6 MJ/kg / 3.6</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>standard published value; no citation logged in references.csv [ESTIMATE - needs source]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>stoichiometry</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>nh3_per_h2_mass_ratio</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.632</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>kg/kg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>N2 + 3 H2 -&gt; 2 NH3; (2 x 17.031)/(3 x 2.016)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>first-principles from standard molar masses M(NH3)=17.031 g/mol, M(H2)=2.016 g/mol; the molar masses themselves are standard values with no citation logged [needs-source: IUPAC/CODATA]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>stoichiometry</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h2_mass_fraction_in_nh3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6.048/34.062, same basis as nh3_per_h2_mass_ratio</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>derived; used to convert NH3 mass back to H2-equivalent</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>nh3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cracking_reaction_enthalpy</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>45.9</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>kJ/mol</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2 NH3 -&gt; N2 + 3 H2 at 298 K, per mol NH3 (endothermic)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>standard formation-enthalpy magnitude; no citation logged. Implies 15.2 MJ per kg H2 = 4.22 kWh/kg-H2 as the thermodynamic floor for cracker heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>corridor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>voyage_distance</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>one-way laden leg, generic basis</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>placeholder; no named corridor fixed yet (decision D1, docs/comparison/00-milestones.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>electrolyser</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>specific_energy_consumption</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>node A; electrical input at battery limit per kg H2 produced, GH2 at 30 barg / 30 C</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>user-specified worked-example default (2026-09-01). Production sits outside KHI's LH2 scope, so no in-repo sourced figure exists. Shared by both chains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>liquefier</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>specific_energy_consumption</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>node B1; per kg H2 liquefied</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>default is the top of KHI's disclosed 8-9 kWh/kg range (conservative); reply Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>liquefier</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>hydrogen_loss</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>node B1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>KHI reply Q15: no H2 losses in the LH2 plant concept under consideration</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>lh2_export_terminal</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>boil_off_rate_at_rest</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>node C1; at-rest LH2 storage</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-supplemental</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>BOR 0.1 %/d on KHI cost-basis slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>lh2_export_terminal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>storage_days</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>node C1; average inventory hold time</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>placeholder hold time; drives BOG mass and therefore BOG-management energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>lh2_export_terminal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bog_reliquefaction_sec</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>node C1/E1; per kg LH2 BOG re-liquefied = 0.438 x liquefaction SEC</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>derived: scales the liquefaction SEC by the ratio of BOG condensation-only ideal work (1.71 kWh/kg) to fresh-feed para-basis ideal work (3.9 kWh/kg), i.e. assumes BOG handling shares the main liquefier's exergetic efficiency. See data/properties/liquefaction.csv and src/lh2/scenario.py BOG_SEC_RATIO. KHI discloses no separate BOG SEC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>lh2_export_terminal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>bog_disposition</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>re-liquefied</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>node C1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>KHI reply Q3: terminal BOG is re-liquefied -&gt; energy penalty, not mass loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>lh2_carrier</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>service_speed</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>node D1; ~16 knots design velocity</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-supplemental</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>160 000 m3 commercial-scale target vessel</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>lh2_carrier</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>voyage_boil_off_rate</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>node D1; laden leg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>KHI discloses no standalone voyage BOR (reply Q23 only states fuel-gas consumption rate = BOR). Placeholder, NOT the 0.1 %/d at-rest terminal figure. research/ holds an unpromoted public figure of ~3.44 %/day (RSER 2026) - deliberately not used here pending promotion approval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>lh2_carrier</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>bog_disposition</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>burned as propulsion fuel</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>node D1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>KHI reply Q23/Q33: BOG feeds a dual-fuel engine, no onboard re-liquefaction -&gt; voyage BOG leaves the chain as H2 mass loss, not as an electrical penalty</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>lh2_import_terminal</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>boil_off_rate_at_rest</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>node E1; at-rest LH2 storage</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-supplemental</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>BOR 0.1 %/d, receiving side</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>lh2_import_terminal</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>storage_days</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>node E1; average inventory hold time</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>placeholder hold time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>lh2_vaporiser</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>regas_heat_duty</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MJ/kg</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>node F1; per kg LH2 vaporised, ORV seawater heat</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>KHI reply Q18. Ambient seawater heat - a thermal duty, not purchased energy; reported separately from the electrical penalty</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>lh2_vaporiser</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>electrical_energy</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.031</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>node F1; cryogenic pump to 30 barg send-out + ORV seawater circulation pump</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>derived first-principles at the default send-out spec (30 barg / 30 C, seawater dT 5 C, head 20 m, pump efficiencies 70%/75%). Same derivation as docs/reports/khi-lh2-reliq-shipping-regas-bfd.html notes 31-32. No KHI or public electrical figure exists for an ORV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>synthesis</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>haber_bosch</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>specific_energy_consumption</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>node B2; per kg NH3 produced - ASU (N2), syngas compression, synthesis loop, refrigeration; electrical</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal Gentari NH3 dataset (decision D4). Excludes the H2 feed itself (node A) and any steam export credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>synthesis</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>haber_bosch</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>hydrogen_loss</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>node B2; purge gas / inerts, net of purge recovery</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>synthesis</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>haber_bosch</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>heat_export_credit</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>node B2; exothermic synthesis heat recoverable as steam</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NOT modelled - carried as an explicit gap. Including it would lower the NH3 chain's net penalty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>nh3_export_terminal</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>boil_off_rate_at_rest</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>node C2; refrigerated NH3 at ~ -33 C, atmospheric</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>nh3_export_terminal</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>storage_days</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>node C2; average inventory hold time</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>placeholder; matched to the LH2 side so the two chains are compared on equal hold time</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>nh3_export_terminal</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>bog_reliquefaction_sec</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>node C2/E2; per kg NH3 BOG re-liquefied (refrigeration compressor)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>service_speed</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>node D2; ~16 knots, mid-size gas carrier</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>placeholder; set close to the LH2 carrier speed so voyage time is not the differentiator by construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>voyage_boil_off_rate</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>node D2; laden leg</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>bog_disposition</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>re-liquefied on board</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>node D2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>placeholder disposition - NH3 carriers may instead burn BOG as fuel; the switch moves the penalty from energy to mass loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nh3_import_terminal</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>boil_off_rate_at_rest</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>node E2; refrigerated NH3 storage</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nh3_import_terminal</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>storage_days</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>node E2; average inventory hold time</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>placeholder; matched to the LH2 side</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cracking</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nh3_cracker</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>hydrogen_self_consumption</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>node F2; H2-equivalent burned for reaction + sensible heat and lost in PSA tail gas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4). Sanity floor: the reaction enthalpy alone is 4.22 kWh/kg-H2 = 12.7% of H2 LHV even if fired with product H2 at 100% efficiency, so a real cracker must exceed 12.7%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cracking</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>nh3_cracker</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>electrical_energy</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>node F2; per kg H2-equivalent entering - PSA, compression, balance of plant</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cracking</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>nh3_cracker</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>reaction_heat_duty</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>node F2; 15.2 MJ per kg H2 produced, from 45.9 kJ/mol-NH3 at 298 K</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>derived from common/nh3/cracking_reaction_enthalpy. Reported for reference only - the heat is supplied by the self-consumption term above, so it is NOT added again to the energy total</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/lh2-database.xlsx
+++ b/data/lh2-database.xlsx
@@ -5573,7 +5573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5906,34 +5906,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>common</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>electrolyser</t>
+          <t>study</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>specific_energy_consumption</t>
+          <t>annual_h2_supply</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>kWh/kg</t>
+          <t>ktpa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>node A; electrical input at battery limit per kg H2 produced, GH2 at 30 barg / 30 C</t>
+          <t>node A; annual H2 supply feeding the study, replaces the 1 kg normalized basis as the headline scale</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -5944,152 +5944,144 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>user-specified worked-example default (2026-09-01). Production sits outside KHI's LH2 scope, so no in-repo sourced figure exists. Shared by both chains.</t>
+          <t>user-specified study basis (2026-09-02). Shared by both chains.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>liquefaction</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>liquefier</t>
+          <t>fleet</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>specific_energy_consumption</t>
+          <t>availability</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>kWh/kg</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>node B1; per kg H2 liquefied</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
+          <t>node D1/D2; shared fleet-wide operational availability</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>default is the top of KHI's disclosed 8-9 kWh/kg range (conservative); reply Q1</t>
+          <t>dry-docking/maintenance/weather margin; not KHI-specific. Same convention as src/lh2/shipping.py fleet_size() default</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>liquefaction</t>
+          <t>production</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>liquefier</t>
+          <t>electrolyser</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hydrogen_loss</t>
+          <t>specific_energy_consumption</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kWh/kg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>node B1</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
+          <t>node A; electrical input at battery limit per kg H2 produced, GH2 at 30 barg / 30 C</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>KHI reply Q15: no H2 losses in the LH2 plant concept under consideration</t>
+          <t>user-specified worked-example default (2026-09-01). Production sits outside KHI's LH2 scope, so no in-repo sourced figure exists. Shared by both chains.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>loading_terminal</t>
+          <t>liquefaction</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lh2_export_terminal</t>
+          <t>liquefier</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>boil_off_rate_at_rest</t>
+          <t>specific_energy_consumption</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>%/day</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>node C1; at-rest LH2 storage</t>
+          <t>node B1; per kg H2 liquefied</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>kawasaki-2026-supplemental</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -6099,52 +6091,56 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>BOR 0.1 %/d on KHI cost-basis slide</t>
+          <t>default is the top of KHI's disclosed 8-9 kWh/kg range (conservative); reply Q1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>loading_terminal</t>
+          <t>liquefaction</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lh2_export_terminal</t>
+          <t>liquefier</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>storage_days</t>
+          <t>hydrogen_loss</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>node C1; average inventory hold time</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>node B1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ASSUMPTION</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>placeholder hold time; drives BOG mass and therefore BOG-management energy</t>
+          <t>KHI reply Q15: no H2 losses in the LH2 plant concept under consideration</t>
         </is>
       </c>
     </row>
@@ -6161,35 +6157,39 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bog_reliquefaction_sec</t>
+          <t>boil_off_rate_at_rest</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>kWh/kg</t>
+          <t>%/day</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>node C1/E1; per kg LH2 BOG re-liquefied = 0.438 x liquefaction SEC</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>node C1; at-rest LH2 storage</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-supplemental</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ASSUMPTION</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>derived: scales the liquefaction SEC by the ratio of BOG condensation-only ideal work (1.71 kWh/kg) to fresh-feed para-basis ideal work (3.9 kWh/kg), i.e. assumes BOG handling shares the main liquefier's exergetic efficiency. See data/properties/liquefaction.csv and src/lh2/scenario.py BOG_SEC_RATIO. KHI discloses no separate BOG SEC.</t>
+          <t>BOR 0.1 %/d on KHI cost-basis slide</t>
         </is>
       </c>
     </row>
@@ -6206,129 +6206,125 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bog_disposition</t>
+          <t>storage_days</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>re-liquefied</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>node C1</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
+          <t>node C1; average inventory hold time</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>KHI reply Q3: terminal BOG is re-liquefied -&gt; energy penalty, not mass loss</t>
+          <t>placeholder hold time; drives BOG mass and therefore BOG-management energy</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>loading_terminal</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lh2_carrier</t>
+          <t>lh2_export_terminal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>service_speed</t>
+          <t>bog_reliquefaction_sec</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>km/h</t>
+          <t>kWh/kg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>node D1; ~16 knots design velocity</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-supplemental</t>
-        </is>
-      </c>
+          <t>node C1/E1; per kg LH2 BOG re-liquefied = 0.438 x liquefaction SEC</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>160 000 m3 commercial-scale target vessel</t>
+          <t>derived: scales the liquefaction SEC by the ratio of BOG condensation-only ideal work (1.71 kWh/kg) to fresh-feed para-basis ideal work (3.9 kWh/kg), i.e. assumes BOG handling shares the main liquefier's exergetic efficiency. See data/properties/liquefaction.csv and src/lh2/scenario.py BOG_SEC_RATIO. KHI discloses no separate BOG SEC.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>loading_terminal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>lh2_carrier</t>
+          <t>lh2_export_terminal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>voyage_boil_off_rate</t>
+          <t>bog_disposition</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>%/day</t>
-        </is>
-      </c>
+          <t>re-liquefied</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>node D1; laden leg</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>node C1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ESTIMATE</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>KHI discloses no standalone voyage BOR (reply Q23 only states fuel-gas consumption rate = BOR). Placeholder, NOT the 0.1 %/d at-rest terminal figure. research/ holds an unpromoted public figure of ~3.44 %/day (RSER 2026) - deliberately not used here pending promotion approval.</t>
+          <t>KHI reply Q3: terminal BOG is re-liquefied -&gt; energy penalty, not mass loss</t>
         </is>
       </c>
     </row>
@@ -6345,25 +6341,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bog_disposition</t>
+          <t>service_speed</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>burned as propulsion fuel</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>node D1</t>
+          <t>node D1; ~16 knots design velocity</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>kawasaki-2026-questionnaire</t>
+          <t>kawasaki-2026-supplemental</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -6373,29 +6373,29 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>KHI reply Q23/Q33: BOG feeds a dual-fuel engine, no onboard re-liquefaction -&gt; voyage BOG leaves the chain as H2 mass loss, not as an electrical penalty</t>
+          <t>disclosed for the 160 000 m3 commercial-scale target vessel; reused here for the 40 000 m3 vessel as no separate speed is disclosed for it</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>regas</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>lh2_import_terminal</t>
+          <t>lh2_carrier</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>boil_off_rate_at_rest</t>
+          <t>voyage_boil_off_rate</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6407,101 +6407,97 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>node E1; at-rest LH2 storage</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-supplemental</t>
-        </is>
-      </c>
+          <t>node D1; laden leg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>BOR 0.1 %/d, receiving side</t>
+          <t>KHI discloses no standalone voyage BOR (reply Q23 only states fuel-gas consumption rate = BOR). Placeholder, NOT the 0.1 %/d at-rest terminal figure. research/ holds an unpromoted public figure of ~3.44 %/day (RSER 2026) - deliberately not used here pending promotion approval.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>regas</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lh2_import_terminal</t>
+          <t>lh2_carrier</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>storage_days</t>
+          <t>bog_disposition</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
+          <t>burned as propulsion fuel</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>node E1; average inventory hold time</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>node D1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ASSUMPTION</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>placeholder hold time</t>
+          <t>KHI reply Q23/Q33: BOG feeds a dual-fuel engine, no onboard re-liquefaction -&gt; voyage BOG leaves the chain as H2 mass loss, not as an electrical penalty</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>regas</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>lh2_vaporiser</t>
+          <t>lh2_carrier</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>regas_heat_duty</t>
+          <t>cargo_capacity</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MJ/kg</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>node F1; per kg LH2 vaporised, ORV seawater heat</t>
+          <t>node D1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -6516,41 +6512,41 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>KHI reply Q18. Ambient seawater heat - a thermal duty, not purchased energy; reported separately from the electrical penalty</t>
+          <t>KHI reply Q29: vessel under construction, same tank tech as Suiso Frontier, no major issues flagged. Replaces the earlier 160 000 m3 commercial-scale-target basis (user direction 2026-09-02).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>regas</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>lh2_vaporiser</t>
+          <t>lh2_carrier</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>electrical_energy</t>
+          <t>cargo_fill_fraction</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>kWh/kg</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>node F1; cryogenic pump to 30 barg send-out + ORV seawater circulation pump</t>
+          <t>node D1; usable fill vs full tank volume</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -6561,258 +6557,266 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>derived first-principles at the default send-out spec (30 barg / 30 C, seawater dT 5 C, head 20 m, pump efficiencies 70%/75%). Same derivation as docs/reports/khi-lh2-reliq-shipping-regas-bfd.html notes 31-32. No KHI or public electrical figure exists for an ORV.</t>
+          <t>placeholder ullage/fill-limit assumption, not KHI-specific</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>synthesis</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>haber_bosch</t>
+          <t>lh2_carrier</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>specific_energy_consumption</t>
+          <t>port_days_per_call</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>kWh/kg</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>node B2; per kg NH3 produced - ASU (N2), syngas compression, synthesis loop, refrigeration; electrical</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>node D1; loading OR unloading, midpoint</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>ESTIMATE</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>placeholder pending the internal Gentari NH3 dataset (decision D4). Excludes the H2 feed itself (node A) and any steam export credit.</t>
+          <t>KHI reply Q27: about 1-1.5 days; midpoint used, same convention as src/lh2/shipping.py KHI_LOAD_UNLOAD_DAYS_MID</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>synthesis</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>haber_bosch</t>
+          <t>lh2_carrier</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>hydrogen_loss</t>
+          <t>cargo_density</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>kg/m3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>node B2; purge gas / inerts, net of purge recovery</t>
+          <t>node D1; LH2 at NBP, fleet-sizing basis</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ESTIMATE</t>
+          <t>needs-source</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>placeholder pending the internal NH3 dataset (D4)</t>
+          <t>mirrors data/properties/lh2-properties.csv density_at_nbp; pending NIST/CODATA citation approval (docs/memory.md open item 4)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>synthesis</t>
+          <t>regas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>haber_bosch</t>
+          <t>lh2_import_terminal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>heat_export_credit</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>boil_off_rate_at_rest</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>kWh/kg</t>
+          <t>%/day</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>node B2; exothermic synthesis heat recoverable as steam</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>node E1; at-rest LH2 storage</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-supplemental</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>needs-source</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>NOT modelled - carried as an explicit gap. Including it would lower the NH3 chain's net penalty.</t>
+          <t>BOR 0.1 %/d, receiving side</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>loading_terminal</t>
+          <t>regas</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nh3_export_terminal</t>
+          <t>lh2_import_terminal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>boil_off_rate_at_rest</t>
+          <t>storage_days</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>%/day</t>
+          <t>day</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>node C2; refrigerated NH3 at ~ -33 C, atmospheric</t>
+          <t>node E1; average inventory hold time</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ESTIMATE</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>placeholder pending the internal NH3 dataset (D4)</t>
+          <t>placeholder hold time</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>loading_terminal</t>
+          <t>regas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nh3_export_terminal</t>
+          <t>lh2_vaporiser</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>storage_days</t>
+          <t>regas_heat_duty</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>MJ/kg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>node C2; average inventory hold time</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>node F1; per kg LH2 vaporised, ORV seawater heat</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>ASSUMPTION</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>placeholder; matched to the LH2 side so the two chains are compared on equal hold time</t>
+          <t>KHI reply Q18. Ambient seawater heat - a thermal duty, not purchased energy; reported separately from the electrical penalty</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>loading_terminal</t>
+          <t>regas</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nh3_export_terminal</t>
+          <t>lh2_vaporiser</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>bog_reliquefaction_sec</t>
+          <t>electrical_energy</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.031</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -6824,52 +6828,60 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>node C2/E2; per kg NH3 BOG re-liquefied (refrigeration compressor)</t>
+          <t>node F1; cryogenic pump to 30 barg send-out + ORV seawater circulation pump</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>ESTIMATE</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>placeholder pending the internal NH3 dataset (D4)</t>
+          <t>derived first-principles at the default send-out spec (30 barg / 30 C, seawater dT 5 C, head 20 m, pump efficiencies 70%/75%). Same derivation as docs/reports/khi-lh2-reliq-shipping-regas-bfd.html notes 31-32. No KHI or public electrical figure exists for an ORV.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>synthesis</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nh3_carrier</t>
+          <t>haber_bosch</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>service_speed</t>
+          <t>specific_energy_consumption</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>km/h</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>node D2; ~16 knots, mid-size gas carrier</t>
+          <t>node B2; per kg NH3 produced - ASU (N2), syngas compression, synthesis loop, refrigeration; electrical</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -6880,41 +6892,41 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>placeholder; set close to the LH2 carrier speed so voyage time is not the differentiator by construction</t>
+          <t>placeholder pending the internal Gentari NH3 dataset (decision D4). Excludes the H2 feed itself (node A) and any steam export credit.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>synthesis</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nh3_carrier</t>
+          <t>haber_bosch</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>voyage_boil_off_rate</t>
+          <t>hydrogen_loss</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>%/day</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>node D2; laden leg</t>
+          <t>node B2; purge gas / inerts, net of purge recovery</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -6932,53 +6944,53 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>synthesis</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nh3_carrier</t>
+          <t>haber_bosch</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bog_disposition</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>re-liquefied on board</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>heat_export_credit</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>node D2</t>
+          <t>node B2; exothermic synthesis heat recoverable as steam</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>ESTIMATE</t>
+          <t>needs-source</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>placeholder disposition - NH3 carriers may instead burn BOG as fuel; the switch moves the penalty from energy to mass loss</t>
+          <t>NOT modelled - carried as an explicit gap. Including it would lower the NH3 chain's net penalty.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>regas</t>
+          <t>loading_terminal</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nh3_import_terminal</t>
+          <t>nh3_export_terminal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -7000,7 +7012,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>node E2; refrigerated NH3 storage</t>
+          <t>node C2; refrigerated NH3 at ~ -33 C, atmospheric</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -7018,12 +7030,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>regas</t>
+          <t>loading_terminal</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nh3_import_terminal</t>
+          <t>nh3_export_terminal</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -7045,7 +7057,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>node E2; average inventory hold time</t>
+          <t>node C2; average inventory hold time</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -7056,49 +7068,41 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>placeholder; matched to the LH2 side</t>
+          <t>placeholder; matched to the LH2 side so the two chains are compared on equal hold time</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cracking</t>
+          <t>loading_terminal</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nh3_cracker</t>
+          <t>nh3_export_terminal</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hydrogen_self_consumption</t>
+          <t>bog_reliquefaction_sec</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>node F2; H2-equivalent burned for reaction + sensible heat and lost in PSA tail gas</t>
+          <t>node C2/E2; per kg NH3 BOG re-liquefied (refrigeration compressor)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -7109,41 +7113,41 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>placeholder pending the internal NH3 dataset (D4). Sanity floor: the reaction enthalpy alone is 4.22 kWh/kg-H2 = 12.7% of H2 LHV even if fired with product H2 at 100% efficiency, so a real cracker must exceed 12.7%.</t>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cracking</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nh3_cracker</t>
+          <t>nh3_carrier</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>electrical_energy</t>
+          <t>service_speed</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>kWh/kg</t>
+          <t>km/h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>node F2; per kg H2-equivalent entering - PSA, compression, balance of plant</t>
+          <t>node D2; ~16 knots, mid-size gas carrier</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -7154,52 +7158,588 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>placeholder pending the internal NH3 dataset (D4)</t>
+          <t>placeholder; set close to the LH2 carrier speed so voyage time is not the differentiator by construction</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cracking</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nh3_cracker</t>
+          <t>nh3_carrier</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>reaction_heat_duty</t>
+          <t>voyage_boil_off_rate</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>kWh/kg</t>
+          <t>%/day</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>node F2; 15.2 MJ per kg H2 produced, from 45.9 kJ/mol-NH3 at 298 K</t>
+          <t>node D2; laden leg, ordinary cargo boil-off only</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>bog_disposition</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>re-liquefied on board</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>node D2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>placeholder disposition - NH3 carriers may instead burn BOG as fuel; the switch moves the penalty from energy to mass loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>cargo_capacity</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>node D2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>user-specified (2026-09-02) mid-size ammonia/LPG-type carrier; not KHI-specific</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>cargo_fill_fraction</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>node D2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>ASSUMPTION</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>derived from common/nh3/cracking_reaction_enthalpy. Reported for reference only - the heat is supplied by the self-consumption term above, so it is NOT added again to the energy total</t>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>placeholder, matched to the LH2 side</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>port_days_per_call</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>node D2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>placeholder, matched to the LH2 side pending an NH3-specific figure</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>cargo_density</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>kg/m3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>node D2; refrigerated liquid NH3 at approx -33 C, 1 atm</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>standard published value; no citation logged in references.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>bunker_fuel_rate</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>node D2; ammonia burned as the carrier's own propulsion fuel, additional to ordinary cargo boil-off; linear in voyage days, not compounded</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>user direction (2026-09-02): cracker is now natural-gas-fired, so the ammonia-vs-delivered-H2 supply ratio (target ~6.5:1) exceeds the pure mass-balance ratio (~5.63:1, common/stoichiometry/nh3_per_h2_mass_ratio); modelled here as ammonia-fuelled marine propulsion, calibrated so defaults reproduce approx 6.5:1 at the default voyage length. Real ammonia-fuelled engines are not yet commercial at scale -- placeholder mechanism, not a disclosed figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>nh3_import_terminal</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>boil_off_rate_at_rest</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>node E2; refrigerated NH3 storage</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>nh3_import_terminal</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>storage_days</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>node E2; average inventory hold time</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>placeholder; matched to the LH2 side</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cracking</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>nh3_cracker</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>process_loss</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>node F2; PSA/purification tail-gas slip only</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4). Replaces the earlier hydrogen_self_consumption mechanic (2026-09-01) now that the cracker is natural-gas-fired (user direction 2026-09-02): reaction heat is purchased NG, not combusted product H2/NH3, so this figure is a much smaller residual than the old 20% -- the old row's 12.7%-of-LHV floor no longer applies to it directly (that floor bounds the NG thermal duty below, not this mass loss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cracking</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>nh3_cracker</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ng_fired_thermal_efficiency</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>node F2; natural-gas-fired heater efficiency converting NG HHV/LHV energy into delivered reaction heat</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>typical industrial fired-heater efficiency; not a disclosed figure. New row (2026-09-02) for the NG-fired cracker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cracking</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>nh3_cracker</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>electrical_energy</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>node F2; per kg H2-equivalent entering - PSA, compression, balance of plant</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cracking</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>nh3_cracker</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>reaction_heat_duty</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>node F2; 15.2 MJ per kg H2 produced, from 45.9 kJ/mol-NH3 at 298 K</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>derived from common/nh3/cracking_reaction_enthalpy. Since 2026-09-02 this IS added to the energy total (scaled by ng_fired_thermal_efficiency): it is the minimum heat the natural-gas-fired heater must deliver, charged as purchased NG energy, not free/self-consumed.</t>
         </is>
       </c>
     </row>

--- a/data/lh2-database.xlsx
+++ b/data/lh2-database.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="references" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="liquefaction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="terminals" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="regas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="lh2_properties" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="lh2_carriers" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="cost_stack" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="chain_energy_defaults" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="references" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="liquefaction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="terminals" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="regas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lh2_properties" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="regulatory_compliance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lh2_carriers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cost_stack" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chain_energy_defaults" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3278,7 +3279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3341,39 +3342,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>regulatory</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>commercial_carrier</t>
+          <t>liquefaction_plant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cargo_capacity</t>
+          <t>permitting_approach</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>160000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
+          <t>Design/permit per applicable local laws &amp; regulations; novel (uncovered) items go through a special evaluation committee</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>commercial-scale target vessel</t>
+          <t>Japan project experience</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>kawasaki-2026-supplemental</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3383,46 +3380,42 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>160000 m3/ship on KHI cost-basis slide</t>
+          <t>KHI reply Q12 (rev0331/GHSB20260406, supersedes reply0304). Outside Japan: KHI states only that a 'similar approach' is expected, 'subject to each country's regulatory regime' -- no non-Japan regime confirmed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>regulatory</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>commercial_carrier</t>
+          <t>liquefaction_plant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>service_speed</t>
+          <t>carbon_intensity_disclosure</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>29.6</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>km/h</t>
-        </is>
-      </c>
+          <t>Feasibility Study necessary; carbon intensity and cost vary with plant size</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>design velocity</t>
+          <t>with RE supply</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>kawasaki-2026-supplemental</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3432,46 +3425,42 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>approx 16 knots</t>
+          <t>KHI reply Q11. Relevant to future carbon-reporting/CBAM-style compliance -- not itself a regulation, but the input KHI ties to one</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>regulatory</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>commercial_carrier</t>
+          <t>shipping_carrier</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fleet_count</t>
+          <t>safety_separation_distance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ship</t>
-        </is>
-      </c>
+          <t>Significantly larger safety separation distances required vs liquid ammonia (no absolute distance disclosed)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Base 2.5B Nm3/y</t>
+          <t>qualitative KHI position</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>kawasaki-2026-supplemental</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3481,657 +3470,229 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2 ships at Base scale</t>
+          <t>KHI reply additional Q36. LH2 classified as a non-toxic, flammable high-pressure gas</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>regulatory</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>commercial_carrier</t>
+          <t>shipping_carrier</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fleet_count</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ship</t>
-        </is>
-      </c>
+          <t>imo_tank_type_classification</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Large 10B Nm3/y</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-supplemental</t>
-        </is>
-      </c>
+          <t>160,000 m3 commercial vessel</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>needs-source</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8 ships at Large scale</t>
+          <t>Not confirmed by KHI or any classification society in-repo. IMO Type A/B/C is an LNG taxonomy discussed generically by RSER 2026 and JMSE 2025 (docs/comparison/khi-vs-literature-lh2-comparison.md Sec.2, Sec.6); no source assigns an IMO type to an LH2 carrier specifically</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>regulatory</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>carrier_40k</t>
+          <t>shipping_carrier</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cargo_capacity</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>40000</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
+          <t>applicable_code_or_standard</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vessel under construction</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
+          <t>hydrogen-fuelled / hydrogen-carrying ships</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>needs-source</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>KHI reply Q29; same tank tech as Suiso Frontier, no major issues</t>
+          <t>IGC Code, IGF Code, and any IMO interim guidelines for LH2 carriers not yet sourced in this repo</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>regulatory</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>suiso_frontier</t>
+          <t>shipping_carrier</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cargo_capacity</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
+          <t>classification_society_approval</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>demonstration vessel</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>kawasaki-hydrogen-activities</t>
-        </is>
-      </c>
+          <t>class approval / approval-in-principle</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>needs-source</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>first LH2 carrier; tank tech basis for scale-up</t>
+          <t>No DNV, ClassNK, Lloyd's Register, or ABS rule set or AiP for LH2 carriers cited in-repo</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>regulatory</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>carrier</t>
+          <t>liquefaction_plant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bog_management</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BOG used as propulsion fuel</t>
-        </is>
-      </c>
+          <t>applicable_code_or_standard</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>dual-fuel engine (in development)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
+          <t>plant design/safety code</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>needs-source</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>KHI reply Q23/Q32; no onboard reliquefaction</t>
+          <t>No liquefaction-plant code (e.g. national high-pressure gas safety law, NFPA 2, ISO hydrogen standards) sourced in-repo beyond KHI's qualitative Q12 answer above</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>regulatory</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>carrier</t>
+          <t>terminal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fuel_gas_consumption_rate</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>equal to BOR</t>
-        </is>
-      </c>
+          <t>applicable_code_or_standard</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>only cargo-tank BOG used as fuel</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
+          <t>export/import terminal siting &amp; process safety</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>needs-source</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>KHI reply Q23; fuel-gas (H2) consumption rate = BOR</t>
+          <t>Exclusion-zone, siting, and process-safety standards for LH2 terminals not yet sourced</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>regulatory</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>carrier</t>
+          <t>chain</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>onboard_reliquefaction</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>not adopted</t>
-        </is>
-      </c>
+          <t>ghg_carbon_border_exposure</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>too much energy + space</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
+          <t>e.g. CBAM-style mechanisms on delivered H2/derivatives</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>needs-source</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>KHI reply Q33</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>filling_ratio_restriction</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>no sloshing impact on BOG</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>KHI reply Q20</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>max_sailing_distance_limit</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>limited by MGO fuel tank</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>not limited by BOG</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>KHI reply Q21</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>mgo_only_pressure_holding</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>several days within MARVS</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>100% MGO regime</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>KHI reply Q26; GCU burns excess BOG above MARVS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>load_unload_duration</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>per vessel call</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>KHI reply Q27; varies with terminal</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>shipyard</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>KHI Sakaide Shipyard</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>construction location</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>KHI reply Q28; lead time longer than LNG carriers</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>scale_up_challenge</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>cargo tank manufacturability</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>toward 160000 m3</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>KHI reply Q29</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>capex_vs_lng</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>significantly higher</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>same-size LNG carrier basis</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>KHI reply Q30/Q31; double-wall tanks/piping, limited suppliers</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>newbuild_cost</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>USD/ship</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>160000 m3 commercial vessel</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>needs-source</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>NOT disclosed by KHI (reply Q31); premium over LNG carrier only qualitative</t>
+          <t>No carbon-border or emissions-reporting regime applicable to the LH2 chain has been researched yet</t>
         </is>
       </c>
     </row>
@@ -4146,7 +3707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4209,39 +3770,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>commercial_carrier</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>cargo_capacity</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
+          <t>commercial-scale target vessel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-supplemental</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -4251,46 +3812,46 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>IAE Gigaton WS WHTC2019 via kawasaki-2026-supplemental; unit inferred (slide unlabelled), ~2019 vintage [needs source: primary]</t>
+          <t>160000 m3/ship on KHI cost-basis slide</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>liquefaction</t>
+          <t>commercial_carrier</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>service_speed</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
+          <t>km/h</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
+          <t>design velocity</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-supplemental</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -4300,46 +3861,46 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>approx 16 knots</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>loading_terminal</t>
+          <t>commercial_carrier</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>fleet_count</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
+          <t>ship</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
+          <t>Base 2.5B Nm3/y</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-supplemental</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -4349,46 +3910,46 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>2 ships at Base scale</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>seaborne_transport</t>
+          <t>commercial_carrier</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>fleet_count</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
+          <t>ship</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
+          <t>Large 10B Nm3/y</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-supplemental</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -4398,46 +3959,46 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>8 ships at Large scale</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>receiving_terminal</t>
+          <t>carrier_40k</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>cargo_capacity</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
+          <t>vessel under construction</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -4447,46 +4008,46 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>KHI reply Q29; same tank tech as Suiso Frontier, no major issues</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dehydrogenation</t>
+          <t>suiso_frontier</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>cargo_capacity</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
+          <t>demonstration vessel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-hydrogen-activities</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -4496,46 +4057,42 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>zero for LH2 (no reconversion step); IAE via KHI [needs source: primary]</t>
+          <t>first LH2 carrier; tank tech basis for scale-up</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>carrier</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>bog_management</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
+          <t>BOG used as propulsion fuel</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
+          <t>dual-fuel engine (in development)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -4545,46 +4102,42 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>KHI reply Q23/Q32; no onboard reliquefaction</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>carrier</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>fuel_gas_consumption_rate</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>37.6</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
+          <t>equal to BOR</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
+          <t>only cargo-tank BOG used as fuel</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4594,46 +4147,42 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>sum of LH2 Base components; reconciliation check</t>
+          <t>KHI reply Q23; fuel-gas (H2) consumption rate = BOR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>carrier</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>onboard_reliquefaction</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
+          <t>not adopted</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>LH2 Large</t>
+          <t>too much energy + space</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4643,46 +4192,42 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>KHI reply Q33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>liquefaction</t>
+          <t>carrier</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>filling_ratio_restriction</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>LH2 Large</t>
+          <t>no sloshing impact on BOG</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4692,46 +4237,42 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>KHI reply Q20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>loading_terminal</t>
+          <t>carrier</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>max_sailing_distance_limit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
+          <t>limited by MGO fuel tank</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>LH2 Large</t>
+          <t>not limited by BOG</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -4741,46 +4282,42 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>KHI reply Q21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>seaborne_transport</t>
+          <t>carrier</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>mgo_only_pressure_holding</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
+          <t>several days within MARVS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>LH2 Large</t>
+          <t>100% MGO regime</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -4790,46 +4327,50 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>KHI reply Q26; GCU burns excess BOG above MARVS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>receiving_terminal</t>
+          <t>carrier</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
+          <t>load_unload_duration</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>LH2 Large</t>
+          <t>per vessel call</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4839,46 +4380,42 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>KHI reply Q27; varies with terminal</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dehydrogenation</t>
+          <t>carrier</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>shipyard</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
+          <t>KHI Sakaide Shipyard</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>LH2 Large</t>
+          <t>construction location</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -4888,46 +4425,42 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>zero for LH2 (no reconversion step); IAE via KHI [needs source: primary]</t>
+          <t>KHI reply Q28; lead time longer than LNG carriers</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>carrier</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>scale_up_challenge</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
+          <t>cargo tank manufacturability</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>LH2 Large</t>
+          <t>toward 160000 m3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -4937,46 +4470,42 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>KHI reply Q29</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>carrier</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>capex_vs_lng</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30.7</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
+          <t>significantly higher</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>LH2 Large</t>
+          <t>same-size LNG carrier basis</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -4986,579 +4515,52 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>sum of LH2 Large components; reconciliation check</t>
+          <t>KHI reply Q30/Q31; double-wall tanks/piping, limited suppliers</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>carrier</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
+          <t>newbuild_cost</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
+          <t>USD/ship</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>LH2 Tech</t>
+          <t>160000 m3 commercial vessel</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>iae-2019-gigaton</t>
+          <t>kawasaki-2026-questionnaire</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>needs-source</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>liquefaction</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>loading_terminal</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>seaborne_transport</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>receiving_terminal</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>dehydrogenation</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>zero for LH2 (no reconversion step); IAE via KHI [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>26.1</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>sum of LH2 Tech components; reconciliation check</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>liquefaction</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>capex_specific</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>reasonable-size plant</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>needs-source</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>NOT disclosed by KHI (reply Q8): Feasibility Study necessary</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>liquefaction</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>opex_specific</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>reasonable-size plant</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>needs-source</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>NOT disclosed by KHI (reply Q9): Feasibility Study necessary</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>receiving_terminal</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>regas_capex_specific</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>reasonable-size terminal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>needs-source</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>not separately disclosed by KHI; only IAE aggregate available</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>newbuild_cost</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>USD/ship</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>160000 m3 vessel</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>needs-source</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>NOT disclosed by KHI (reply Q31)</t>
+          <t>NOT disclosed by KHI (reply Q31); premium over LNG carrier only qualitative</t>
         </is>
       </c>
     </row>
@@ -5573,6 +4575,1433 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>segment</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>IAE Gigaton WS WHTC2019 via kawasaki-2026-supplemental; unit inferred (slide unlabelled), ~2019 vintage [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>seaborne_transport</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>receiving_terminal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dehydrogenation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>zero for LH2 (no reconversion step); IAE via KHI [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>37.6</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>sum of LH2 Base components; reconciliation check</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>seaborne_transport</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>receiving_terminal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dehydrogenation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>zero for LH2 (no reconversion step); IAE via KHI [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>30.7</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>sum of LH2 Large components; reconciliation check</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>seaborne_transport</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>receiving_terminal</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>dehydrogenation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>zero for LH2 (no reconversion step); IAE via KHI [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>sum of LH2 Tech components; reconciliation check</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>capex_specific</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>reasonable-size plant</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>NOT disclosed by KHI (reply Q8): Feasibility Study necessary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>opex_specific</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>reasonable-size plant</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NOT disclosed by KHI (reply Q9): Feasibility Study necessary</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>receiving_terminal</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>regas_capex_specific</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>reasonable-size terminal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>not separately disclosed by KHI; only IAE aggregate available</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>carrier</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>newbuild_cost</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>USD/ship</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>160000 m3 vessel</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>NOT disclosed by KHI (reply Q31)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/lh2-database.xlsx
+++ b/data/lh2-database.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="references" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="liquefaction" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="terminals" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="regas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lh2_properties" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="regulatory_compliance" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lh2_carriers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cost_stack" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chain_energy_defaults" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="references" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="liquefaction" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="terminals" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="regas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="lh2_properties" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="regulatory_compliance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="lh2_carriers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="nh3_carriers" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kakinada_hamburg_route" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="cost_stack" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="chain_energy_defaults" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -717,6 +719,3614 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>segment</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>IAE Gigaton WS WHTC2019 via kawasaki-2026-supplemental; unit inferred (slide unlabelled), ~2019 vintage [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>seaborne_transport</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>receiving_terminal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dehydrogenation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>zero for LH2 (no reconversion step); IAE via KHI [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>37.6</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>LH2 Base</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>sum of LH2 Base components; reconciliation check</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>seaborne_transport</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>receiving_terminal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dehydrogenation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>zero for LH2 (no reconversion step); IAE via KHI [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>30.7</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>LH2 Large</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>sum of LH2 Large components; reconciliation check</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>seaborne_transport</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>receiving_terminal</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>dehydrogenation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>zero for LH2 (no reconversion step); IAE via KHI [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>supply_cost</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>JPY/Nm3</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>LH2 Tech</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>iae-2019-gigaton</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>sum of LH2 Tech components; reconciliation check</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>capex_specific</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>reasonable-size plant</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>NOT disclosed by KHI (reply Q8): Feasibility Study necessary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>opex_specific</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>reasonable-size plant</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NOT disclosed by KHI (reply Q9): Feasibility Study necessary</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>receiving_terminal</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>regas_capex_specific</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>reasonable-size terminal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>not separately disclosed by KHI; only IAE aggregate available</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>carrier</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>newbuild_cost</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>USD/ship</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>160000 m3 vessel</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>NOT disclosed by KHI (reply Q31)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>segment</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lower_heating_value</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>33.333</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>120 MJ/kg / 3.6; energy basis for every efficiency in this table</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>mirrors data/properties/lh2-properties.csv; pending NIST/ISO citation approval (docs/memory.md open item 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nh3</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>lower_heating_value</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5.167</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>18.6 MJ/kg / 3.6</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>standard published value; no citation logged in references.csv [ESTIMATE - needs source]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>stoichiometry</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>nh3_per_h2_mass_ratio</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.632</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>kg/kg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>N2 + 3 H2 -&gt; 2 NH3; (2 x 17.031)/(3 x 2.016)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>first-principles from standard molar masses M(NH3)=17.031 g/mol, M(H2)=2.016 g/mol; the molar masses themselves are standard values with no citation logged [needs-source: IUPAC/CODATA]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>stoichiometry</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h2_mass_fraction_in_nh3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6.048/34.062, same basis as nh3_per_h2_mass_ratio</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>derived; used to convert NH3 mass back to H2-equivalent</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>nh3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cracking_reaction_enthalpy</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>45.9</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>kJ/mol</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2 NH3 -&gt; N2 + 3 H2 at 298 K, per mol NH3 (endothermic)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>standard formation-enthalpy magnitude; no citation logged. Implies 15.2 MJ per kg H2 = 4.22 kWh/kg-H2 as the thermodynamic floor for cracker heat</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>corridor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>voyage_distance</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>one-way laden leg, generic basis</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>placeholder; no named corridor fixed yet (decision D1, docs/comparison/00-milestones.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>annual_h2_supply</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ktpa</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>node A; annual H2 supply feeding the study, replaces the 1 kg normalized basis as the headline scale</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>user-specified study basis (2026-09-02). Shared by both chains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fleet</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>availability</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>node D1/D2; shared fleet-wide operational availability</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>dry-docking/maintenance/weather margin; not KHI-specific. Same convention as src/lh2/shipping.py fleet_size() default</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>electrolyser</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>specific_energy_consumption</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>node A; electrical input at battery limit per kg H2 produced, GH2 at 30 barg / 30 C</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>user-specified worked-example default (2026-09-01). Production sits outside KHI's LH2 scope, so no in-repo sourced figure exists. Shared by both chains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>liquefier</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>specific_energy_consumption</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>node B1; per kg H2 liquefied</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>default is the top of KHI's disclosed 8-9 kWh/kg range (conservative); reply Q1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>liquefaction</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>liquefier</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hydrogen_loss</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>node B1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>KHI reply Q15: no H2 losses in the LH2 plant concept under consideration</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>lh2_export_terminal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>boil_off_rate_at_rest</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>node C1; at-rest LH2 storage</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-supplemental</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>BOR 0.1 %/d on KHI cost-basis slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>lh2_export_terminal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>storage_days</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>node C1; average inventory hold time</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>placeholder hold time; drives BOG mass and therefore BOG-management energy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>lh2_export_terminal</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>bog_reliquefaction_sec</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>node C1/E1; per kg LH2 BOG re-liquefied = 0.438 x liquefaction SEC</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>derived: scales the liquefaction SEC by the ratio of BOG condensation-only ideal work (1.71 kWh/kg) to fresh-feed para-basis ideal work (3.9 kWh/kg), i.e. assumes BOG handling shares the main liquefier's exergetic efficiency. See data/properties/liquefaction.csv and src/lh2/scenario.py BOG_SEC_RATIO. KHI discloses no separate BOG SEC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>lh2_export_terminal</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>bog_disposition</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>re-liquefied</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>node C1</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>KHI reply Q3: terminal BOG is re-liquefied -&gt; energy penalty, not mass loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>lh2_carrier</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>service_speed</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>node D1; ~16 knots design velocity</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-supplemental</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>disclosed for the 160 000 m3 commercial-scale target vessel; reused here for the 40 000 m3 vessel as no separate speed is disclosed for it</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>lh2_carrier</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>voyage_boil_off_rate</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>node D1; laden leg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>KHI discloses no standalone voyage BOR (reply Q23 only states fuel-gas consumption rate = BOR). Placeholder, NOT the 0.1 %/d at-rest terminal figure. research/ holds an unpromoted public figure of ~3.44 %/day (RSER 2026) - deliberately not used here pending promotion approval.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>lh2_carrier</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bog_disposition</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>burned as propulsion fuel</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>node D1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>KHI reply Q23/Q33: BOG feeds a dual-fuel engine, no onboard re-liquefaction -&gt; voyage BOG leaves the chain as H2 mass loss, not as an electrical penalty</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>lh2_carrier</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>cargo_capacity</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>node D1</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>KHI reply Q29: vessel under construction, same tank tech as Suiso Frontier, no major issues flagged. Replaces the earlier 160 000 m3 commercial-scale-target basis (user direction 2026-09-02).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>lh2_carrier</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>cargo_fill_fraction</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>node D1; usable fill vs full tank volume</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>placeholder ullage/fill-limit assumption, not KHI-specific</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>lh2_carrier</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>port_days_per_call</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>node D1; loading OR unloading, midpoint</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>KHI reply Q27: about 1-1.5 days; midpoint used, same convention as src/lh2/shipping.py KHI_LOAD_UNLOAD_DAYS_MID</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>lh2_carrier</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>cargo_density</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>70.8</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>kg/m3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>node D1; LH2 at NBP, fleet-sizing basis</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>mirrors data/properties/lh2-properties.csv density_at_nbp; pending NIST/CODATA citation approval (docs/memory.md open item 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>lh2_import_terminal</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>boil_off_rate_at_rest</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>node E1; at-rest LH2 storage</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-supplemental</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>BOR 0.1 %/d, receiving side</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>lh2_import_terminal</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>storage_days</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>node E1; average inventory hold time</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>placeholder hold time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>lh2_vaporiser</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>regas_heat_duty</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MJ/kg</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>node F1; per kg LH2 vaporised, ORV seawater heat</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>kawasaki-2026-questionnaire</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>KHI reply Q18. Ambient seawater heat - a thermal duty, not purchased energy; reported separately from the electrical penalty</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>lh2_vaporiser</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>electrical_energy</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.031</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>node F1; cryogenic pump to 30 barg send-out + ORV seawater circulation pump</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>derived first-principles at the default send-out spec (30 barg / 30 C, seawater dT 5 C, head 20 m, pump efficiencies 70%/75%). Same derivation as docs/reports/khi-lh2-reliq-shipping-regas-bfd.html notes 31-32. No KHI or public electrical figure exists for an ORV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>synthesis</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>haber_bosch</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>specific_energy_consumption</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>node B2; per kg NH3 produced - ASU (N2), syngas compression, synthesis loop, refrigeration; electrical</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal Gentari NH3 dataset (decision D4). Excludes the H2 feed itself (node A) and any steam export credit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>synthesis</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>haber_bosch</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>hydrogen_loss</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>node B2; purge gas / inerts, net of purge recovery</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>synthesis</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>haber_bosch</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>heat_export_credit</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>node B2; exothermic synthesis heat recoverable as steam</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NOT modelled - carried as an explicit gap. Including it would lower the NH3 chain's net penalty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nh3_export_terminal</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>boil_off_rate_at_rest</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>node C2; refrigerated NH3 at ~ -33 C, atmospheric</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nh3_export_terminal</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>storage_days</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>node C2; average inventory hold time</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>placeholder; matched to the LH2 side so the two chains are compared on equal hold time</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>loading_terminal</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nh3_export_terminal</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>bog_reliquefaction_sec</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>node C2/E2; per kg NH3 BOG re-liquefied (refrigeration compressor)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>service_speed</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>node D2; ~16 knots, mid-size gas carrier</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>placeholder; set close to the LH2 carrier speed so voyage time is not the differentiator by construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>voyage_boil_off_rate</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>node D2; laden leg, ordinary cargo boil-off only</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>bog_disposition</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>re-liquefied on board</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>node D2</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>placeholder disposition - NH3 carriers may instead burn BOG as fuel; the switch moves the penalty from energy to mass loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>cargo_capacity</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>node D2</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>user-specified (2026-09-02) mid-size ammonia/LPG-type carrier; not KHI-specific</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>cargo_fill_fraction</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>node D2</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>placeholder, matched to the LH2 side</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>port_days_per_call</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>node D2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>placeholder, matched to the LH2 side pending an NH3-specific figure</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>cargo_density</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>kg/m3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>node D2; refrigerated liquid NH3 at approx -33 C, 1 atm</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>standard published value; no citation logged in references.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>nh3_carrier</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>bunker_fuel_rate</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>node D2; ammonia burned as the carrier's own propulsion fuel, additional to ordinary cargo boil-off; linear in voyage days, not compounded</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>user direction (2026-09-02): cracker is now natural-gas-fired, so the ammonia-vs-delivered-H2 supply ratio (target ~6.5:1) exceeds the pure mass-balance ratio (~5.63:1, common/stoichiometry/nh3_per_h2_mass_ratio); modelled here as ammonia-fuelled marine propulsion, calibrated so defaults reproduce approx 6.5:1 at the default voyage length. Real ammonia-fuelled engines are not yet commercial at scale -- placeholder mechanism, not a disclosed figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>nh3_import_terminal</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>boil_off_rate_at_rest</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>node E2; refrigerated NH3 storage</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>regas</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>nh3_import_terminal</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>storage_days</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>node E2; average inventory hold time</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>placeholder; matched to the LH2 side</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cracking</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>nh3_cracker</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>process_loss</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>node F2; PSA/purification tail-gas slip only</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4). Replaces the earlier hydrogen_self_consumption mechanic (2026-09-01) now that the cracker is natural-gas-fired (user direction 2026-09-02): reaction heat is purchased NG, not combusted product H2/NH3, so this figure is a much smaller residual than the old 20% -- the old row's 12.7%-of-LHV floor no longer applies to it directly (that floor bounds the NG thermal duty below, not this mass loss).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cracking</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>nh3_cracker</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ng_fired_thermal_efficiency</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>node F2; natural-gas-fired heater efficiency converting NG HHV/LHV energy into delivered reaction heat</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>typical industrial fired-heater efficiency; not a disclosed figure. New row (2026-09-02) for the NG-fired cracker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cracking</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>nh3_cracker</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>electrical_energy</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>node F2; per kg H2-equivalent entering - PSA, compression, balance of plant</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>placeholder pending the internal NH3 dataset (D4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cracking</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>nh3_cracker</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>reaction_heat_duty</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>kWh/kg</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>node F2; 15.2 MJ per kg H2 produced, from 45.9 kJ/mol-NH3 at 298 K</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>derived from common/nh3/cracking_reaction_enthalpy. Since 2026-09-02 this IS added to the energy total (scaled by ng_fired_thermal_efficiency): it is the minimum heat the natural-gas-fired heater must deliver, charged as purchased NG energy, not free/self-consumed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4575,7 +8185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4638,1356 +8248,319 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>carrier_24k</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>cargo_capacity</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
+          <t>24 kcbm fully-refrigerated ammonia carrier</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>IAE Gigaton WS WHTC2019 via kawasaki-2026-supplemental; unit inferred (slide unlabelled), ~2019 vintage [needs source: primary]</t>
+          <t>user-specified vessel for the Kakinada-Hamburg shipping comparison (2026-09-07); this is a specific study vessel, distinct from the generic 40000 m3 placeholder in data/carriers/chain-energy-defaults.csv used by the whole-chain energy ledger</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>liquefaction</t>
+          <t>carrier_24k</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>cargo_density</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>682</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
+          <t>kg/m3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
+          <t>refrigerated liquid NH3 at approx -33 C, 1 atm, fully-refrigerated cargo condition (user-confirmed 2026-09-07)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>standard published value for refrigerated liquid ammonia; no primary citation logged in references.csv yet. Same figure already used as a placeholder in data/carriers/chain-energy-defaults.csv (2026-09-02)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>loading_terminal</t>
+          <t>carrier_24k</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>service_speed</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>24.076</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
+          <t>km/h</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
+          <t>user-specified service speed = 13 knots</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>user-specified (2026-09-07); 13 kn x 1.852 = 24.076 km/h. Materially slower than the LH2 40k carrier's 29.6 km/h (KHI, kawasaki-2026-supplemental) -- a key driver of the shipping comparison</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>seaborne_transport</t>
+          <t>carrier_24k</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>voyage_boil_off_rate</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>%/day</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
+          <t>laden leg, ordinary cargo boil-off</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>user selected the 0.1-0.2 %/day range (2026-09-07); midpoint used as the point default. No NH3-specific technical dataset exists yet (decision D4) -- treat as a placeholder, same caveat status as the LH2 carrier's own 0.2 %/day voyage-BOR estimate</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>receiving_terminal</t>
+          <t>carrier_24k</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>bog_disposition</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
+          <t>re-liquefied on board</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
+          <t>onboard reliquefaction plant</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
+          <t>user-specified (2026-09-07): boil-off gas is condensed back into the cargo tank -- an ENERGY cost (refrigeration compressor duty), not a cargo mass loss. Contrasts with the LH2 40k carrier, which burns BOG as propulsion fuel (KHI reply Q23/Q33) and therefore loses cargo mass. No onboard-reliquefaction SEC (kWh/kg) figure has been supplied yet -- carried as an explicit gap in this analysis, not fabricated</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dehydrogenation</t>
+          <t>carrier_24k</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>port_days_per_call</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
+          <t>day</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
+          <t>loading OR unloading, per call</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>zero for LH2 (no reconversion step); IAE via KHI [needs source: primary]</t>
+          <t>user-specified (2026-09-07), set equal to the LH2 carrier's disclosed 1-1.5 day range (KHI reply Q27) for direct comparability</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>shipping</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>carrier_24k</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>supply_cost</t>
+          <t>cargo_fill_fraction</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JPY/Nm3</t>
+          <t>%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>LH2 Base</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
+          <t>usable fill vs full tank volume</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>37.6</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>LH2 Base</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>sum of LH2 Base components; reconciliation check</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>LH2 Large</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>liquefaction</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>LH2 Large</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>loading_terminal</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>LH2 Large</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>seaborne_transport</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>LH2 Large</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>receiving_terminal</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>LH2 Large</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>dehydrogenation</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>LH2 Large</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>zero for LH2 (no reconversion step); IAE via KHI [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>LH2 Large</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>IAE via KHI; unit inferred JPY/Nm3 ~2019 [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>LH2 Large</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>sum of LH2 Large components; reconciliation check</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>liquefaction</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>loading_terminal</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>seaborne_transport</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>receiving_terminal</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>dehydrogenation</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>zero for LH2 (no reconversion step); IAE via KHI [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>IAE via KHI; technological-progress case [needs source: primary]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>supply_cost</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>26.1</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>JPY/Nm3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>LH2 Tech</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>iae-2019-gigaton</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>sum of LH2 Tech components; reconciliation check</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>liquefaction</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>capex_specific</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>reasonable-size plant</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>needs-source</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>NOT disclosed by KHI (reply Q8): Feasibility Study necessary</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>liquefaction</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>opex_specific</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>reasonable-size plant</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>needs-source</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>NOT disclosed by KHI (reply Q9): Feasibility Study necessary</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>receiving_terminal</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>regas_capex_specific</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>reasonable-size terminal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>needs-source</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>not separately disclosed by KHI; only IAE aggregate available</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>newbuild_cost</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>USD/ship</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>160000 m3 vessel</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>needs-source</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>NOT disclosed by KHI (reply Q31)</t>
+          <t>matched to the LH2 carrier's own fill-fraction placeholder for comparability; not NH3-specific, no source</t>
         </is>
       </c>
     </row>
@@ -6002,7 +8575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6065,79 +8638,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>corridor</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>h2</t>
+          <t>kakinada_hamburg</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lower_heating_value</t>
+          <t>distance_one_way_suez</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33.333</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>kWh/kg</t>
+          <t>km</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>120 MJ/kg / 3.6; energy basis for every efficiency in this table</t>
+          <t>Kakinada (INKAK) to Hamburg (DEHAM), via Suez Canal + Bab-el-Mandeb + Gibraltar (classic shortest route)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>needs-source</t>
+          <t>ESTIMATE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>mirrors data/properties/lh2-properties.csv; pending NIST/ISO citation approval (docs/memory.md open item 4)</t>
+          <t>first-principles great-circle waypoint sum (Kakinada -&gt; S. tip Sri Lanka -&gt; Bab-el-Mandeb -&gt; Suez -&gt; Port Said -&gt; Gibraltar -&gt; Hamburg), +8% margin for canal transit/coastal routing. NOT a primary AIS/charterer distance-table figure -- WebFetch to searoutes.com and similar distance calculators is blocked by this environment's egress policy, and WebSearch could not surface the exact published figure. [needs source: primary AIS/route-planning tool] if precision matters for a final economics run</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>corridor</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nh3</t>
+          <t>kakinada_hamburg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lower_heating_value</t>
+          <t>distance_one_way_cape</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.167</t>
+          <t>21200</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>kWh/kg</t>
+          <t>km</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>18.6 MJ/kg / 3.6</t>
+          <t>Kakinada (INKAK) to Hamburg (DEHAM), via Cape of Good Hope (bypassing Suez/Red Sea)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -6148,41 +8721,37 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>standard published value; no citation logged in references.csv [ESTIMATE - needs source]</t>
+          <t>first-principles great-circle waypoint sum (Kakinada -&gt; S. tip Sri Lanka -&gt; Cape of Good Hope -&gt; Gibraltar -&gt; Hamburg), +8% margin. Cross-checked: the same waypoint method applied to Karachi-&gt;Hamburg reproduces a public WebSearch-surfaced figure of 11,076 NM to within 2% (11,317 NM computed) when routed via the Cape -- which also indicates that public figure is itself a Cape-route number, not Suez, consistent with carriers avoiding the Red Sea/Suez amid the security situation as of 2026. USER-SELECTED as the primary basis for this shipping comparison (2026-09-07); the Suez figure is retained for reference/sensitivity, not deleted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>corridor</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>stoichiometry</t>
+          <t>kakinada_hamburg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nh3_per_h2_mass_ratio</t>
+          <t>route_basis_selected</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.632</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>kg/kg</t>
-        </is>
-      </c>
+          <t>cape_of_good_hope</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>N2 + 3 H2 -&gt; 2 NH3; (2 x 17.031)/(3 x 2.016)</t>
+          <t>which of the two distances above is used as this study's primary case</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -6193,1982 +8762,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>first-principles from standard molar masses M(NH3)=17.031 g/mol, M(H2)=2.016 g/mol; the molar masses themselves are standard values with no citation logged [needs-source: IUPAC/CODATA]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>stoichiometry</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>h2_mass_fraction_in_nh3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>17.75</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>6.048/34.062, same basis as nh3_per_h2_mass_ratio</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>derived; used to convert NH3 mass back to H2-equivalent</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>nh3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>cracking_reaction_enthalpy</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>45.9</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>kJ/mol</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2 NH3 -&gt; N2 + 3 H2 at 298 K, per mol NH3 (endothermic)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>needs-source</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>standard formation-enthalpy magnitude; no citation logged. Implies 15.2 MJ per kg H2 = 4.22 kWh/kg-H2 as the thermodynamic floor for cracker heat</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>corridor</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>voyage_distance</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>km</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>one-way laden leg, generic basis</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>placeholder; no named corridor fixed yet (decision D1, docs/comparison/00-milestones.md)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>study</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>annual_h2_supply</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ktpa</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>node A; annual H2 supply feeding the study, replaces the 1 kg normalized basis as the headline scale</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>user-specified study basis (2026-09-02). Shared by both chains.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>fleet</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>availability</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>node D1/D2; shared fleet-wide operational availability</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>dry-docking/maintenance/weather margin; not KHI-specific. Same convention as src/lh2/shipping.py fleet_size() default</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>electrolyser</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>specific_energy_consumption</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>kWh/kg</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>node A; electrical input at battery limit per kg H2 produced, GH2 at 30 barg / 30 C</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>user-specified worked-example default (2026-09-01). Production sits outside KHI's LH2 scope, so no in-repo sourced figure exists. Shared by both chains.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>liquefaction</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>liquefier</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>specific_energy_consumption</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>kWh/kg</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>node B1; per kg H2 liquefied</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>default is the top of KHI's disclosed 8-9 kWh/kg range (conservative); reply Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>liquefaction</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>liquefier</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>hydrogen_loss</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>node B1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>KHI reply Q15: no H2 losses in the LH2 plant concept under consideration</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>loading_terminal</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>lh2_export_terminal</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>boil_off_rate_at_rest</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>%/day</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>node C1; at-rest LH2 storage</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-supplemental</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>BOR 0.1 %/d on KHI cost-basis slide</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>loading_terminal</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>lh2_export_terminal</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>storage_days</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>node C1; average inventory hold time</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>placeholder hold time; drives BOG mass and therefore BOG-management energy</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>loading_terminal</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>lh2_export_terminal</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>bog_reliquefaction_sec</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>3.94</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>kWh/kg</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>node C1/E1; per kg LH2 BOG re-liquefied = 0.438 x liquefaction SEC</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>derived: scales the liquefaction SEC by the ratio of BOG condensation-only ideal work (1.71 kWh/kg) to fresh-feed para-basis ideal work (3.9 kWh/kg), i.e. assumes BOG handling shares the main liquefier's exergetic efficiency. See data/properties/liquefaction.csv and src/lh2/scenario.py BOG_SEC_RATIO. KHI discloses no separate BOG SEC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>loading_terminal</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>lh2_export_terminal</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>bog_disposition</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>re-liquefied</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>node C1</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>KHI reply Q3: terminal BOG is re-liquefied -&gt; energy penalty, not mass loss</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>lh2_carrier</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>service_speed</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>km/h</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>node D1; ~16 knots design velocity</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-supplemental</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>disclosed for the 160 000 m3 commercial-scale target vessel; reused here for the 40 000 m3 vessel as no separate speed is disclosed for it</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>lh2_carrier</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>voyage_boil_off_rate</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>%/day</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>node D1; laden leg</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>KHI discloses no standalone voyage BOR (reply Q23 only states fuel-gas consumption rate = BOR). Placeholder, NOT the 0.1 %/d at-rest terminal figure. research/ holds an unpromoted public figure of ~3.44 %/day (RSER 2026) - deliberately not used here pending promotion approval.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>lh2_carrier</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>bog_disposition</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>burned as propulsion fuel</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>node D1</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>KHI reply Q23/Q33: BOG feeds a dual-fuel engine, no onboard re-liquefaction -&gt; voyage BOG leaves the chain as H2 mass loss, not as an electrical penalty</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>lh2_carrier</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>cargo_capacity</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>40000</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>node D1</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>KHI reply Q29: vessel under construction, same tank tech as Suiso Frontier, no major issues flagged. Replaces the earlier 160 000 m3 commercial-scale-target basis (user direction 2026-09-02).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>lh2_carrier</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>cargo_fill_fraction</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>node D1; usable fill vs full tank volume</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>placeholder ullage/fill-limit assumption, not KHI-specific</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>lh2_carrier</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>port_days_per_call</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>node D1; loading OR unloading, midpoint</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>KHI reply Q27: about 1-1.5 days; midpoint used, same convention as src/lh2/shipping.py KHI_LOAD_UNLOAD_DAYS_MID</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>lh2_carrier</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>cargo_density</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>70.8</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>kg/m3</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>node D1; LH2 at NBP, fleet-sizing basis</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>needs-source</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>mirrors data/properties/lh2-properties.csv density_at_nbp; pending NIST/CODATA citation approval (docs/memory.md open item 4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>regas</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>lh2_import_terminal</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>boil_off_rate_at_rest</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>%/day</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>node E1; at-rest LH2 storage</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-supplemental</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>BOR 0.1 %/d, receiving side</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>regas</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>lh2_import_terminal</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>storage_days</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>node E1; average inventory hold time</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>placeholder hold time</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>regas</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>lh2_vaporiser</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>regas_heat_duty</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>MJ/kg</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>node F1; per kg LH2 vaporised, ORV seawater heat</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>kawasaki-2026-questionnaire</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>KHI reply Q18. Ambient seawater heat - a thermal duty, not purchased energy; reported separately from the electrical penalty</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>regas</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>lh2_vaporiser</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>electrical_energy</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>0.031</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>kWh/kg</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>node F1; cryogenic pump to 30 barg send-out + ORV seawater circulation pump</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>derived first-principles at the default send-out spec (30 barg / 30 C, seawater dT 5 C, head 20 m, pump efficiencies 70%/75%). Same derivation as docs/reports/khi-lh2-reliq-shipping-regas-bfd.html notes 31-32. No KHI or public electrical figure exists for an ORV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>synthesis</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>haber_bosch</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>specific_energy_consumption</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>kWh/kg</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>node B2; per kg NH3 produced - ASU (N2), syngas compression, synthesis loop, refrigeration; electrical</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>placeholder pending the internal Gentari NH3 dataset (decision D4). Excludes the H2 feed itself (node A) and any steam export credit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>synthesis</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>haber_bosch</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>hydrogen_loss</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>node B2; purge gas / inerts, net of purge recovery</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>placeholder pending the internal NH3 dataset (D4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>synthesis</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>haber_bosch</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>heat_export_credit</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>kWh/kg</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>node B2; exothermic synthesis heat recoverable as steam</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>needs-source</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>NOT modelled - carried as an explicit gap. Including it would lower the NH3 chain's net penalty.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>loading_terminal</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>nh3_export_terminal</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>boil_off_rate_at_rest</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>%/day</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>node C2; refrigerated NH3 at ~ -33 C, atmospheric</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>placeholder pending the internal NH3 dataset (D4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>loading_terminal</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>nh3_export_terminal</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>storage_days</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>node C2; average inventory hold time</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>placeholder; matched to the LH2 side so the two chains are compared on equal hold time</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>loading_terminal</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>nh3_export_terminal</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>bog_reliquefaction_sec</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>kWh/kg</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>node C2/E2; per kg NH3 BOG re-liquefied (refrigeration compressor)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>placeholder pending the internal NH3 dataset (D4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>nh3_carrier</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>service_speed</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>km/h</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>node D2; ~16 knots, mid-size gas carrier</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>placeholder; set close to the LH2 carrier speed so voyage time is not the differentiator by construction</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>nh3_carrier</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>voyage_boil_off_rate</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>%/day</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>node D2; laden leg, ordinary cargo boil-off only</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>placeholder pending the internal NH3 dataset (D4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>nh3_carrier</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>bog_disposition</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>re-liquefied on board</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>node D2</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>placeholder disposition - NH3 carriers may instead burn BOG as fuel; the switch moves the penalty from energy to mass loss</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>nh3_carrier</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>cargo_capacity</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>40000</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>node D2</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>user-specified (2026-09-02) mid-size ammonia/LPG-type carrier; not KHI-specific</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>nh3_carrier</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>cargo_fill_fraction</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>node D2</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>placeholder, matched to the LH2 side</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>nh3_carrier</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>port_days_per_call</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>node D2</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>placeholder, matched to the LH2 side pending an NH3-specific figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>nh3_carrier</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>cargo_density</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>kg/m3</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>node D2; refrigerated liquid NH3 at approx -33 C, 1 atm</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>standard published value; no citation logged in references.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>shipping</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>nh3_carrier</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>bunker_fuel_rate</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>%/day</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>node D2; ammonia burned as the carrier's own propulsion fuel, additional to ordinary cargo boil-off; linear in voyage days, not compounded</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>user direction (2026-09-02): cracker is now natural-gas-fired, so the ammonia-vs-delivered-H2 supply ratio (target ~6.5:1) exceeds the pure mass-balance ratio (~5.63:1, common/stoichiometry/nh3_per_h2_mass_ratio); modelled here as ammonia-fuelled marine propulsion, calibrated so defaults reproduce approx 6.5:1 at the default voyage length. Real ammonia-fuelled engines are not yet commercial at scale -- placeholder mechanism, not a disclosed figure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>regas</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>nh3_import_terminal</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>boil_off_rate_at_rest</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>%/day</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>node E2; refrigerated NH3 storage</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>placeholder pending the internal NH3 dataset (D4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>regas</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>nh3_import_terminal</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>storage_days</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>node E2; average inventory hold time</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>placeholder; matched to the LH2 side</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>cracking</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>nh3_cracker</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>process_loss</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>node F2; PSA/purification tail-gas slip only</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>placeholder pending the internal NH3 dataset (D4). Replaces the earlier hydrogen_self_consumption mechanic (2026-09-01) now that the cracker is natural-gas-fired (user direction 2026-09-02): reaction heat is purchased NG, not combusted product H2/NH3, so this figure is a much smaller residual than the old 20% -- the old row's 12.7%-of-LHV floor no longer applies to it directly (that floor bounds the NG thermal duty below, not this mass loss).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>cracking</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>nh3_cracker</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>ng_fired_thermal_efficiency</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>node F2; natural-gas-fired heater efficiency converting NG HHV/LHV energy into delivered reaction heat</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>typical industrial fired-heater efficiency; not a disclosed figure. New row (2026-09-02) for the NG-fired cracker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>cracking</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>nh3_cracker</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>electrical_energy</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>kWh/kg</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>node F2; per kg H2-equivalent entering - PSA, compression, balance of plant</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>ESTIMATE</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>placeholder pending the internal NH3 dataset (D4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>cracking</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>nh3_cracker</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>reaction_heat_duty</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>kWh/kg</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>node F2; 15.2 MJ per kg H2 produced, from 45.9 kJ/mol-NH3 at 298 K</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>derived from common/nh3/cracking_reaction_enthalpy. Since 2026-09-02 this IS added to the energy total (scaled by ng_fired_thermal_efficiency): it is the minimum heat the natural-gas-fired heater must deliver, charged as purchased NG energy, not free/self-consumed.</t>
+          <t>explicit user decision (2026-09-07) to reflect current operating reality rather than the classic shortest route</t>
         </is>
       </c>
     </row>

--- a/data/lh2-database.xlsx
+++ b/data/lh2-database.xlsx
@@ -8185,7 +8185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8561,6 +8561,354 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>matched to the LH2 carrier's own fill-fraction placeholder for comparability; not NH3-specific, no source</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>carrier_24k</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bunker_fuel_consumption</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>t/day</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>VLSFO burn rate under way, laden</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>user-specified (2026-09-07). Sets the propulsion duty for BOTH carriers in the shipping comparison: the LH2 carrier is charged the same duty so its boil-off-as-fuel can be tested against a like-for-like demand. Approximation -- the LH2 carrier is a larger hull at higher speed, so its true demand is probably higher; flagged rather than scaled, since no power curve is held for either vessel</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>carrier_24k</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bunker_fuel_type</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VLSFO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>very low sulphur fuel oil</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>user-specified (2026-09-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>vlsfo_lower_heating_value</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>40.2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MJ/kg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>marine residual fuel LHV</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>40.2 MJ/kg is the marine convention for heavy/very-low-sulphur fuel oil (the IMO MEPC EEDI/CII figure for HFO). No primary citation logged in references.csv yet [needs source: IMO MEPC guideline]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bog_engine_efficiency_ratio</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>kg/kg</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>thermal efficiency burning BOG vs burning the liquid bunker fuel in the same engine</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>set to parity because no dual-fuel engine efficiency data is held for either fuel. Exposed as a live input in docs/reports/lh2-vs-nh3-shipping-studies.html so it is never silently assumed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>carrier_24k</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>reliq_genset_efficiency</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>shipboard generator thermal efficiency converting bunker fuel into the electricity that drives the reliquefaction plant</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>typical medium-speed marine genset efficiency; not vessel-specific and not sourced. Needed to express NH3 reliquefaction electricity as a physical fuel cost on the same basis as the LH2 carrier boil-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h2_gwp100</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>kg/kg</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>warming potential of vented hydrogen, 100-year basis, CO2-equivalent</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>published indirect-GWP estimates for H2 cluster near this value with a wide uncertainty band. No primary citation logged [needs source: IPCC AR6 / Warwick et al.]. Applies ONLY to hydrogen actually released to atmosphere -- KHI reply Q26 describes a gas combustion unit burning excess BOG above MARVS, in which case the H2 is combusted to water and this figure does not apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h2_price</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>delivered hydrogen value used to price cargo boil-off as a premium fuel</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NOT set -- a live user input in the shipping-studies artifact, with no default asserted. The whole LH2-vs-NH3 bunker economics turns on it; the artifact reports the breakeven price instead of assuming one</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>vlsfo_price</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>USD/t</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bunker fuel price</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>needs-source</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NOT set -- a live user input in the shipping-studies artifact, no default asserted</t>
         </is>
       </c>
     </row>

--- a/data/lh2-database.xlsx
+++ b/data/lh2-database.xlsx
@@ -7422,7 +7422,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>160000 m3/ship on KHI cost-basis slide</t>
+          <t>160000 m3/ship on KHI cost-basis slide. STUDY DEFAULT for the shipping comparison since 2026-09-07 (user direction, replacing the 40000 m3 vessel): the disclosed 29.6 km/h service speed was given for THIS ship, so pairing them is more internally consistent</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8909,6 +8909,51 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>NOT set -- a live user input in the shipping-studies artifact, no default asserted</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>lh2_carrier_160k</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>bunker_fuel_consumption</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>t/day</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>VLSFO-equivalent propulsion duty charged to the LH2 carrier</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>carried over from the user's ammonia-vessel figure (2026-09-07) so both carriers sit on one basis. NOT a disclosed figure for the 160000 m3 vessel, and almost certainly low for a hull that size: at ~100 t/day (roughly 4x, matching the 4x cargo scale-up from the 40000 m3 ship) the boil-off coverage falls from ~258% to ~64% and the surplus disappears entirely. The whole surplus/venting finding turns on this number -- exposed as a live input in the artifact [needs source: vessel power curve or design fuel rate]</t>
         </is>
       </c>
     </row>

--- a/data/lh2-database.xlsx
+++ b/data/lh2-database.xlsx
@@ -8185,7 +8185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8954,6 +8954,59 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>carried over from the user's ammonia-vessel figure (2026-09-07) so both carriers sit on one basis. NOT a disclosed figure for the 160000 m3 vessel, and almost certainly low for a hull that size: at ~100 t/day (roughly 4x, matching the 4x cargo scale-up from the 40000 m3 ship) the boil-off coverage falls from ~258% to ~64% and the surplus disappears entirely. The whole surplus/venting finding turns on this number -- exposed as a live input in the artifact [needs source: vessel power curve or design fuel rate]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>carrier_scenarios</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>cargo_capacity_options</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>24000; 40000; 60000; 90000</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>24000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>selectable NH3 vessel sizes in the shipping-studies artifact</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>user-requested scenario set (2026-09-08). 24000 is the originally specified vessel; 40000/60000/90000 correspond to mid-size, large and VLGC-scale gas carriers -- general industry size bands, NOT figures from this repository. The largest ammonia carriers in service are around 87000 m3 [ESTIMATE - needs source: vessel register]. Note the stated 25 t/day propulsion duty belongs to the 24000 m3 hull; the artifact offers a size^(2/3) scaled suggestion for the others rather than carrying 25 t/day across silently</t>
         </is>
       </c>
     </row>
